--- a/output/pdf_financials_xlsx/VVTM.xlsx
+++ b/output/pdf_financials_xlsx/VVTM.xlsx
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.335</v>
       </c>
     </row>
     <row r="92">
@@ -2934,7 +2934,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.047</v>
       </c>

--- a/output/pdf_financials_xlsx/VVTM.xlsx
+++ b/output/pdf_financials_xlsx/VVTM.xlsx
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -3322,7 +3322,11 @@
           <t>Increase in long-term deposit</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.002</v>
       </c>
